--- a/KURIKULUM2026_REVISI/006_DISTRIBUSI_DAN_PANDUAN_MK_PEMINATAN_MBKM.xlsx
+++ b/KURIKULUM2026_REVISI/006_DISTRIBUSI_DAN_PANDUAN_MK_PEMINATAN_MBKM.xlsx
@@ -569,7 +569,7 @@
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>• STI-626 Deep Learning (+P) (3)</t>
+          <t>• STI-726 Deep Learning (+P) (3)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
@@ -579,7 +579,7 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>• STI-627 Platform Eng (3)</t>
+          <t>• STI-727 Platform Eng (3)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
@@ -699,7 +699,7 @@
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>• STI-624 Integrasi AI (3)</t>
+          <t>• STI-726 Integrasi AI (3)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -709,7 +709,7 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>• STI-625 Smart City (2)</t>
+          <t>• STI-727 Smart City (2)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
